--- a/can_map.xlsx
+++ b/can_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\CPT\Проекты\2023-3-2 - Опытный поезд\4_Этапы проекта\1. СКУ\Алгоритм\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tamas\Projects\can_monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD891D8-2F58-4AE9-BB04-3D9438D0EBAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418DB66F-E512-4130-9358-FFF9817F6D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Адрессация шины 1" sheetId="2" r:id="rId1"/>
@@ -23,12 +23,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="267">
   <si>
     <t>Устройство</t>
   </si>
@@ -557,14 +560,6 @@
     <t>ОТВЕТ НА НАСТРОЙКУ</t>
   </si>
   <si>
-    <t>0,1В/бит
-little-endian</t>
-  </si>
-  <si>
-    <t>1кОм/бит
-little-endian</t>
-  </si>
-  <si>
     <t>СОСТОЯНИЯ 100 мс</t>
   </si>
   <si>
@@ -848,9 +843,6 @@
     </r>
   </si>
   <si>
-    <t>10В/бит</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -876,9 +868,6 @@
     </r>
   </si>
   <si>
-    <t>10А/бит</t>
-  </si>
-  <si>
     <t>0/1</t>
   </si>
   <si>
@@ -1086,9 +1075,6 @@
       <t xml:space="preserve">
 код состояния систем</t>
     </r>
-  </si>
-  <si>
-    <t>номер парсинга</t>
   </si>
   <si>
     <t>ДАННЫЕ ПО НАПРЯЖЕНИЮ
@@ -1357,9 +1343,6 @@
     <t>Парсинг данных</t>
   </si>
   <si>
-    <t>передаваемое значение</t>
-  </si>
-  <si>
     <t>…</t>
   </si>
   <si>
@@ -1857,17 +1840,74 @@
   <si>
     <t>32-й бит - RESERVE</t>
   </si>
+  <si>
+    <t>2-8-й биты - номер парсинга</t>
+  </si>
+  <si>
+    <t>10В/ед</t>
+  </si>
+  <si>
+    <t>10А/ед</t>
+  </si>
+  <si>
+    <t>0,1В/ед
+little-endian</t>
+  </si>
+  <si>
+    <t>1кОм/ед
+little-endian</t>
+  </si>
+  <si>
+    <r>
+      <t>1В/ед
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>°</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.65"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>С/ед
+прямой код</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1-й бит - 0 - парсинг значений напряжений ячеек / 1 - парсинг значений температур ячеек </t>
+  </si>
+  <si>
+    <t>передаваемое значение на байт</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1965,6 +2005,19 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12.65"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2179,7 +2232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2190,13 +2243,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2216,27 +2269,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2264,303 +2317,312 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2853,444 +2915,444 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
-        <v>136</v>
+      <c r="A2" s="57" t="s">
+        <v>131</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="56"/>
+      <c r="A4" s="59"/>
       <c r="B4" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C4" s="27"/>
     </row>
     <row r="5" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>148</v>
-      </c>
       <c r="C6" s="25" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
     <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="56"/>
+      <c r="A8" s="59"/>
       <c r="B8" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C8" s="27"/>
     </row>
     <row r="9" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="60"/>
+      <c r="B11" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="60"/>
+      <c r="B12" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="61"/>
+      <c r="B13" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="26"/>
+    </row>
+    <row r="14" spans="1:4" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B14" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="60"/>
+      <c r="B15" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C15" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="60"/>
+      <c r="B16" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="60"/>
+      <c r="B17" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="60"/>
+      <c r="B18" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="61"/>
+      <c r="B19" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="29"/>
+    </row>
+    <row r="20" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="B20" s="26" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
+      <c r="C20" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="60"/>
+      <c r="B21" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="60"/>
+      <c r="B22" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="57"/>
-      <c r="B11" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C22" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="57"/>
-      <c r="B12" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="58"/>
-      <c r="B13" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C13" s="26"/>
-    </row>
-    <row r="14" spans="1:4" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="54" t="s">
+    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="60"/>
+      <c r="B23" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="57"/>
-      <c r="B15" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="57"/>
-      <c r="B16" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="26" t="s">
+      <c r="C23" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="60"/>
+      <c r="B24" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="57"/>
-      <c r="B17" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="57"/>
-      <c r="B18" s="26" t="s">
+      <c r="C24" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="D24" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="61"/>
+      <c r="B25" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="29"/>
+    </row>
+    <row r="26" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="57" t="s">
         <v>163</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="58"/>
-      <c r="B19" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="29"/>
-    </row>
-    <row r="20" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="57"/>
-      <c r="B21" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="57"/>
-      <c r="B22" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="57"/>
-      <c r="B23" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="57"/>
-      <c r="B24" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="58"/>
-      <c r="B25" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="C25" s="29"/>
-    </row>
-    <row r="26" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="54" t="s">
-        <v>168</v>
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="25"/>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="55"/>
+      <c r="A27" s="58"/>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
       <c r="D27" s="15"/>
     </row>
     <row r="28" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="56"/>
+      <c r="A28" s="59"/>
       <c r="B28" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C28" s="27"/>
     </row>
     <row r="29" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="54" t="s">
-        <v>170</v>
+      <c r="A29" s="57" t="s">
+        <v>165</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="25"/>
     </row>
     <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="55"/>
+      <c r="A30" s="58"/>
       <c r="B30" s="26"/>
       <c r="C30" s="26"/>
       <c r="D30" s="15"/>
     </row>
     <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="56"/>
+      <c r="A31" s="59"/>
       <c r="B31" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C31" s="27"/>
     </row>
     <row r="32" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="54" t="s">
-        <v>169</v>
+      <c r="A32" s="57" t="s">
+        <v>164</v>
       </c>
       <c r="B32" s="26"/>
       <c r="C32" s="25"/>
     </row>
     <row r="33" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="55"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
       <c r="D33" s="15"/>
     </row>
     <row r="34" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="56"/>
+      <c r="A34" s="59"/>
       <c r="B34" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C34" s="27"/>
     </row>
     <row r="35" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="54" t="s">
-        <v>171</v>
+      <c r="A35" s="57" t="s">
+        <v>166</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="25"/>
     </row>
     <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="55"/>
+      <c r="A36" s="58"/>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
       <c r="D36" s="15"/>
     </row>
     <row r="37" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="56"/>
+      <c r="A37" s="59"/>
       <c r="B37" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C37" s="27"/>
     </row>
     <row r="38" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="54" t="s">
-        <v>172</v>
+      <c r="A38" s="57" t="s">
+        <v>167</v>
       </c>
       <c r="B38" s="26"/>
       <c r="C38" s="25"/>
     </row>
     <row r="39" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="55"/>
+      <c r="A39" s="58"/>
       <c r="B39" s="26"/>
       <c r="C39" s="26"/>
       <c r="D39" s="15"/>
     </row>
     <row r="40" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="56"/>
+      <c r="A40" s="59"/>
       <c r="B40" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C40" s="27"/>
     </row>
     <row r="41" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="54" t="s">
-        <v>151</v>
+      <c r="A41" s="57" t="s">
+        <v>146</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="55"/>
+      <c r="A42" s="58"/>
       <c r="B42" s="26"/>
       <c r="C42" s="26"/>
       <c r="D42" s="15"/>
     </row>
     <row r="43" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="56"/>
+      <c r="A43" s="59"/>
       <c r="B43" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C43" s="27"/>
     </row>
     <row r="44" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="54" t="s">
-        <v>152</v>
+      <c r="A44" s="57" t="s">
+        <v>147</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="55"/>
+      <c r="A45" s="58"/>
       <c r="B45" s="30"/>
       <c r="C45" s="26"/>
     </row>
     <row r="46" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="56"/>
+      <c r="A46" s="59"/>
       <c r="B46" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C46" s="27"/>
     </row>
     <row r="47" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="54" t="s">
-        <v>173</v>
+      <c r="A47" s="57" t="s">
+        <v>168</v>
       </c>
       <c r="B47" s="26"/>
       <c r="C47" s="25"/>
       <c r="D47" s="15"/>
     </row>
     <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="55"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="30"/>
       <c r="C48" s="26"/>
     </row>
     <row r="49" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="56"/>
+      <c r="A49" s="59"/>
       <c r="B49" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C49" s="27"/>
     </row>
@@ -3316,7 +3378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA88"/>
+  <dimension ref="A1:AA89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="5" bestFit="1" customWidth="1"/>
@@ -3325,7 +3387,7 @@
     <col min="4" max="4" width="6.5703125" style="31" customWidth="1"/>
     <col min="5" max="5" width="45" style="31" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="12"/>
+    <col min="7" max="7" width="9.85546875" style="12" customWidth="1"/>
     <col min="9" max="9" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3351,19 +3413,19 @@
       </c>
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="63" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="71" t="s">
+      <c r="B2" s="64" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="60">
+      <c r="D2" s="70">
         <v>0</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="71" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="31"/>
@@ -3372,96 +3434,96 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="62"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="59"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="72"/>
       <c r="F3" s="31"/>
       <c r="G3" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="59"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="72"/>
       <c r="F4" s="31"/>
       <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="62"/>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="59"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="72"/>
       <c r="F5" s="31"/>
       <c r="G5" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="62"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="60">
+      <c r="A6" s="63"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="70">
         <v>1</v>
       </c>
-      <c r="E6" s="72" t="s">
+      <c r="E6" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="59" t="s">
-        <v>115</v>
+      <c r="F6" s="72" t="s">
+        <v>111</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="62"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="60"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="70"/>
       <c r="G7" s="7" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="62"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="60"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="70"/>
       <c r="G8" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="62"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="60"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="70"/>
       <c r="G9" s="7" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="62"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="60">
+      <c r="A10" s="63"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="70">
         <v>2</v>
       </c>
-      <c r="E10" s="69" t="s">
+      <c r="E10" s="71" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="31"/>
@@ -3470,39 +3532,39 @@
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="62"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
       <c r="F11" s="31"/>
       <c r="G11" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="62"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
       <c r="F12" s="32"/>
       <c r="G12" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="71" t="s">
+      <c r="A13" s="63"/>
+      <c r="B13" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="68">
+      <c r="D13" s="69">
         <v>0</v>
       </c>
-      <c r="E13" s="66" t="s">
+      <c r="E13" s="67" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="4"/>
@@ -3511,101 +3573,101 @@
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="62"/>
-      <c r="B14" s="64"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="65"/>
       <c r="C14" s="78"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="67"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="68"/>
       <c r="F14" s="31"/>
       <c r="G14" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="62"/>
-      <c r="B15" s="64"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="65"/>
       <c r="C15" s="78"/>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="69" t="s">
+      <c r="E15" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="59" t="s">
-        <v>63</v>
+      <c r="F15" s="72" t="s">
+        <v>263</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="62"/>
-      <c r="B16" s="64"/>
+      <c r="A16" s="63"/>
+      <c r="B16" s="65"/>
       <c r="C16" s="78"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="60"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="70"/>
       <c r="G16" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="62"/>
-      <c r="B17" s="64"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="65"/>
       <c r="C17" s="78"/>
-      <c r="D17" s="70" t="s">
+      <c r="D17" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="69" t="s">
+      <c r="E17" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="59" t="s">
-        <v>63</v>
+      <c r="F17" s="72" t="s">
+        <v>263</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="62"/>
-      <c r="B18" s="64"/>
+      <c r="A18" s="63"/>
+      <c r="B18" s="65"/>
       <c r="C18" s="78"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="60"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="70"/>
       <c r="G18" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="62"/>
-      <c r="B19" s="64"/>
+      <c r="A19" s="63"/>
+      <c r="B19" s="65"/>
       <c r="C19" s="78"/>
-      <c r="D19" s="60">
+      <c r="D19" s="70">
         <v>5</v>
       </c>
-      <c r="E19" s="69" t="s">
+      <c r="E19" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="60"/>
+      <c r="F19" s="70"/>
       <c r="G19" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="62"/>
-      <c r="B20" s="64"/>
+      <c r="A20" s="63"/>
+      <c r="B20" s="65"/>
       <c r="C20" s="78"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="60"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="70"/>
       <c r="G20" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="62"/>
-      <c r="B21" s="65"/>
+      <c r="A21" s="63"/>
+      <c r="B21" s="66"/>
       <c r="C21" s="79"/>
       <c r="D21" s="31" t="s">
         <v>28</v>
@@ -3613,20 +3675,20 @@
       <c r="E21" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="39" t="s">
-        <v>62</v>
+      <c r="F21" s="38" t="s">
+        <v>262</v>
       </c>
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="62"/>
-      <c r="B22" s="63" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="71" t="s">
+      <c r="A22" s="63"/>
+      <c r="B22" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="68">
+      <c r="D22" s="69">
         <v>0</v>
       </c>
       <c r="E22" s="85" t="s">
@@ -3638,24 +3700,24 @@
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="69"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="71"/>
       <c r="F23" s="31"/>
       <c r="G23" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="62"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="60">
+      <c r="A24" s="63"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="70">
         <v>1</v>
       </c>
-      <c r="E24" s="69" t="s">
+      <c r="E24" s="71" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="31"/>
@@ -3664,10 +3726,10 @@
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="62"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="73"/>
+      <c r="A25" s="63"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="76"/>
       <c r="E25" s="86"/>
       <c r="F25" s="31"/>
       <c r="G25" s="7" t="s">
@@ -3675,11 +3737,11 @@
       </c>
     </row>
     <row r="26" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="62"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="71" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="74" t="s">
         <v>40</v>
       </c>
       <c r="D26" s="4">
@@ -3694,7 +3756,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="62"/>
+      <c r="A27" s="63"/>
       <c r="B27" s="81"/>
       <c r="C27" s="78"/>
       <c r="D27" s="31" t="s">
@@ -3711,10 +3773,10 @@
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="62"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="81"/>
       <c r="C28" s="78"/>
-      <c r="D28" s="60">
+      <c r="D28" s="70">
         <v>3</v>
       </c>
       <c r="E28" s="31" t="s">
@@ -3726,10 +3788,10 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="62"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="81"/>
       <c r="C29" s="78"/>
-      <c r="D29" s="60"/>
+      <c r="D29" s="70"/>
       <c r="E29" s="31" t="s">
         <v>43</v>
       </c>
@@ -3739,16 +3801,16 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="62"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="81"/>
       <c r="C30" s="78"/>
-      <c r="D30" s="70" t="s">
+      <c r="D30" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="60" t="s">
+      <c r="E30" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="72" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="11" t="s">
@@ -3756,22 +3818,22 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="62"/>
+      <c r="A31" s="63"/>
       <c r="B31" s="82"/>
       <c r="C31" s="79"/>
       <c r="D31" s="84"/>
-      <c r="E31" s="73"/>
+      <c r="E31" s="76"/>
       <c r="F31" s="83"/>
       <c r="G31" s="11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="62"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="71" t="s">
+      <c r="C32" s="74" t="s">
         <v>55</v>
       </c>
       <c r="D32" s="4">
@@ -3786,7 +3848,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="62"/>
+      <c r="A33" s="63"/>
       <c r="B33" s="81"/>
       <c r="C33" s="78"/>
       <c r="D33" s="31" t="s">
@@ -3803,13 +3865,13 @@
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="62"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="81"/>
       <c r="C34" s="78"/>
-      <c r="D34" s="60">
+      <c r="D34" s="70">
         <v>3</v>
       </c>
-      <c r="E34" s="59" t="s">
+      <c r="E34" s="72" t="s">
         <v>58</v>
       </c>
       <c r="F34" s="31"/>
@@ -3818,470 +3880,459 @@
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="62"/>
+      <c r="A35" s="63"/>
       <c r="B35" s="82"/>
       <c r="C35" s="79"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="59"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="72"/>
       <c r="F35" s="31"/>
       <c r="G35" s="22" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="103" t="s">
-        <v>101</v>
-      </c>
-      <c r="B36" s="63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="71" t="s">
-        <v>207</v>
-      </c>
-      <c r="D36" s="68">
+      <c r="A36" s="105" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="74" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="69">
         <v>0</v>
       </c>
-      <c r="E36" s="74" t="s">
-        <v>121</v>
-      </c>
-      <c r="F36" s="68"/>
-      <c r="G36" s="50" t="s">
-        <v>215</v>
+      <c r="E36" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" s="69"/>
+      <c r="G36" s="49" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="104"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="64"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
+      <c r="A37" s="106"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
       <c r="G37" s="7" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="104"/>
-      <c r="B38" s="64"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="60"/>
+      <c r="A38" s="106"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
       <c r="G38" s="7" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="104"/>
-      <c r="B39" s="64"/>
-      <c r="C39" s="64"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
+      <c r="A39" s="106"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
       <c r="G39" s="7" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="104"/>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="60">
+      <c r="A40" s="106"/>
+      <c r="B40" s="65"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="70">
         <v>1</v>
       </c>
-      <c r="E40" s="75" t="s">
-        <v>122</v>
-      </c>
-      <c r="F40" s="59" t="s">
+      <c r="E40" s="104" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="106"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="106"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="106"/>
+      <c r="B43" s="65"/>
+      <c r="C43" s="65"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="106"/>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="21" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="106"/>
+      <c r="B45" s="65"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="106"/>
+      <c r="B46" s="66"/>
+      <c r="C46" s="66"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="111"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="106"/>
+      <c r="B47" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="G40" s="21" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="104"/>
-      <c r="B41" s="64"/>
-      <c r="C41" s="64"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="60"/>
-      <c r="G41" s="21" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="104"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="75"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="104"/>
-      <c r="B43" s="64"/>
-      <c r="C43" s="64"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="60"/>
-      <c r="G43" s="21" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="104"/>
-      <c r="B44" s="64"/>
-      <c r="C44" s="64"/>
-      <c r="D44" s="60"/>
-      <c r="E44" s="75"/>
-      <c r="F44" s="60"/>
-      <c r="G44" s="21" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="104"/>
-      <c r="B45" s="64"/>
-      <c r="C45" s="64"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="75"/>
-      <c r="F45" s="60"/>
-      <c r="G45" s="21" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="104"/>
-      <c r="B46" s="65"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="76"/>
-      <c r="F46" s="73"/>
-      <c r="G46" s="21" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="104"/>
-      <c r="B47" s="102" t="s">
-        <v>120</v>
-      </c>
-      <c r="C47" s="71" t="s">
-        <v>208</v>
-      </c>
-      <c r="D47" s="68">
+      <c r="C47" s="74" t="s">
+        <v>202</v>
+      </c>
+      <c r="D47" s="69">
         <v>0</v>
       </c>
-      <c r="E47" s="74" t="s">
-        <v>116</v>
+      <c r="E47" s="99" t="s">
+        <v>112</v>
       </c>
       <c r="F47" s="97"/>
       <c r="G47" s="20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="104"/>
+      <c r="A48" s="106"/>
       <c r="B48" s="81"/>
       <c r="C48" s="78"/>
-      <c r="D48" s="60"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="60"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="70"/>
       <c r="G48" s="21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="104"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="106"/>
       <c r="B49" s="81"/>
       <c r="C49" s="78"/>
-      <c r="D49" s="60"/>
-      <c r="E49" s="75"/>
-      <c r="F49" s="60"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="70"/>
       <c r="G49" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="104"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="106"/>
       <c r="B50" s="81"/>
       <c r="C50" s="78"/>
-      <c r="D50" s="60"/>
-      <c r="E50" s="75"/>
-      <c r="F50" s="60"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="70"/>
       <c r="G50" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="104"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="106"/>
       <c r="B51" s="81"/>
       <c r="C51" s="78"/>
-      <c r="D51" s="60"/>
-      <c r="E51" s="75"/>
-      <c r="F51" s="60"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="70"/>
       <c r="G51" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="104"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="106"/>
       <c r="B52" s="81"/>
       <c r="C52" s="78"/>
-      <c r="D52" s="60"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="60"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="70"/>
       <c r="G52" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="104"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="106"/>
       <c r="B53" s="81"/>
       <c r="C53" s="78"/>
-      <c r="D53" s="60"/>
-      <c r="E53" s="75"/>
-      <c r="F53" s="60"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="70"/>
       <c r="G53" s="21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="104"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="106"/>
       <c r="B54" s="81"/>
       <c r="C54" s="78"/>
-      <c r="D54" s="60">
+      <c r="D54" s="70">
         <v>1</v>
       </c>
-      <c r="E54" s="75" t="s">
-        <v>103</v>
-      </c>
-      <c r="F54" s="60"/>
+      <c r="E54" s="104" t="s">
+        <v>99</v>
+      </c>
+      <c r="F54" s="70"/>
       <c r="G54" s="7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="104"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="106"/>
       <c r="B55" s="81"/>
-      <c r="C55" s="64"/>
-      <c r="D55" s="60"/>
-      <c r="E55" s="75"/>
-      <c r="F55" s="60"/>
+      <c r="C55" s="65"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="70"/>
       <c r="G55" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="3" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="104"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" s="3" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="106"/>
       <c r="B56" s="82"/>
-      <c r="C56" s="65"/>
+      <c r="C56" s="66"/>
       <c r="D56" s="32">
         <v>2</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F56" s="32"/>
       <c r="G56" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="2" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="104"/>
-      <c r="B57" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="C57" s="71" t="s">
-        <v>209</v>
-      </c>
-      <c r="D57" s="4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" s="2" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="106"/>
+      <c r="B57" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="74" t="s">
+        <v>203</v>
+      </c>
+      <c r="D57" s="69">
         <v>0</v>
       </c>
-      <c r="E57" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F57" s="40"/>
-      <c r="G57" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="2" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="104"/>
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E58" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="F58" s="41"/>
-      <c r="G58" s="23" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="104"/>
-      <c r="B59" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="C59" s="71" t="s">
-        <v>210</v>
-      </c>
-      <c r="D59" s="68">
+      <c r="E57" s="99" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" s="39"/>
+      <c r="G57" s="139" t="s">
+        <v>265</v>
+      </c>
+      <c r="H57" s="140"/>
+      <c r="I57" s="140"/>
+      <c r="J57" s="140"/>
+      <c r="K57" s="140"/>
+      <c r="L57" s="140"/>
+    </row>
+    <row r="58" spans="1:12" s="2" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="106"/>
+      <c r="B58" s="78"/>
+      <c r="C58" s="78"/>
+      <c r="D58" s="70"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="53" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="2" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="106"/>
+      <c r="B59" s="65"/>
+      <c r="C59" s="65"/>
+      <c r="D59" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="G59" s="23" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="106"/>
+      <c r="B60" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="74" t="s">
+        <v>204</v>
+      </c>
+      <c r="D60" s="69">
         <v>0</v>
       </c>
-      <c r="E59" s="108" t="s">
-        <v>98</v>
-      </c>
-      <c r="F59" s="4"/>
-      <c r="G59" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="104"/>
-      <c r="B60" s="64"/>
-      <c r="C60" s="78"/>
-      <c r="D60" s="60"/>
-      <c r="E60" s="72"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="104"/>
-      <c r="B61" s="64"/>
+      <c r="E60" s="110" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="106"/>
+      <c r="B61" s="65"/>
       <c r="C61" s="78"/>
-      <c r="D61" s="60"/>
-      <c r="E61" s="72"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="75"/>
       <c r="F61" s="31"/>
       <c r="G61" s="24" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="104"/>
-      <c r="B62" s="64"/>
-      <c r="C62" s="64"/>
-      <c r="D62" s="60"/>
-      <c r="E62" s="72"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="106"/>
+      <c r="B62" s="65"/>
+      <c r="C62" s="78"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="75"/>
       <c r="F62" s="31"/>
       <c r="G62" s="24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="104"/>
-      <c r="B63" s="64"/>
-      <c r="C63" s="64"/>
-      <c r="D63" s="60">
-        <v>1</v>
-      </c>
-      <c r="E63" s="72" t="s">
-        <v>100</v>
-      </c>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="106"/>
+      <c r="B63" s="65"/>
+      <c r="C63" s="65"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="75"/>
       <c r="F63" s="31"/>
-      <c r="G63" s="106" t="s">
-        <v>99</v>
-      </c>
-      <c r="H63" s="106"/>
-      <c r="I63" s="106"/>
-    </row>
-    <row r="64" spans="1:9" s="3" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="105"/>
+      <c r="G63" s="24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="106"/>
       <c r="B64" s="65"/>
       <c r="C64" s="65"/>
-      <c r="D64" s="73"/>
-      <c r="E64" s="73"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-    </row>
-    <row r="65" spans="1:27" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="98" t="s">
+      <c r="D64" s="70">
+        <v>1</v>
+      </c>
+      <c r="E64" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="F64" s="31"/>
+      <c r="G64" s="108" t="s">
+        <v>95</v>
+      </c>
+      <c r="H64" s="108"/>
+      <c r="I64" s="108"/>
+    </row>
+    <row r="65" spans="1:27" s="3" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="107"/>
+      <c r="B65" s="66"/>
+      <c r="C65" s="66"/>
+      <c r="D65" s="76"/>
+      <c r="E65" s="76"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="109"/>
+      <c r="H65" s="109"/>
+      <c r="I65" s="109"/>
+    </row>
+    <row r="66" spans="1:27" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="100" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="B65" s="80" t="s">
-        <v>64</v>
-      </c>
-      <c r="C65" s="71" t="s">
-        <v>79</v>
-      </c>
-      <c r="D65" s="68">
+      <c r="D66" s="69">
         <v>0</v>
       </c>
-      <c r="E65" s="94" t="s">
-        <v>78</v>
-      </c>
-      <c r="F65" s="68"/>
-      <c r="G65" s="90" t="s">
-        <v>130</v>
-      </c>
-      <c r="H65" s="90"/>
-      <c r="I65" s="90"/>
-      <c r="J65" s="90"/>
-      <c r="K65" s="90"/>
-      <c r="L65" s="90"/>
-      <c r="M65" s="90"/>
-      <c r="N65" s="90"/>
-      <c r="O65" s="90"/>
-      <c r="P65" s="90"/>
-      <c r="Q65" s="90"/>
-      <c r="R65" s="90"/>
-      <c r="S65" s="90"/>
-      <c r="T65" s="90"/>
-      <c r="U65" s="90"/>
-      <c r="V65" s="90"/>
-      <c r="W65" s="90"/>
-      <c r="X65" s="90"/>
-      <c r="Y65" s="90"/>
-      <c r="Z65" s="90"/>
-      <c r="AA65" s="90"/>
-    </row>
-    <row r="66" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="99"/>
-      <c r="B66" s="81"/>
-      <c r="C66" s="78"/>
-      <c r="D66" s="60"/>
-      <c r="E66" s="92"/>
-      <c r="F66" s="60"/>
-      <c r="G66" s="91"/>
-      <c r="H66" s="91"/>
-      <c r="I66" s="91"/>
-      <c r="J66" s="91"/>
-      <c r="K66" s="91"/>
-      <c r="L66" s="91"/>
-      <c r="M66" s="91"/>
-      <c r="N66" s="91"/>
-      <c r="O66" s="91"/>
-      <c r="P66" s="91"/>
-      <c r="Q66" s="91"/>
-      <c r="R66" s="91"/>
-      <c r="S66" s="91"/>
-      <c r="T66" s="91"/>
-      <c r="U66" s="91"/>
-      <c r="V66" s="91"/>
-      <c r="W66" s="91"/>
-      <c r="X66" s="91"/>
-      <c r="Y66" s="91"/>
-      <c r="Z66" s="91"/>
-      <c r="AA66" s="91"/>
+      <c r="E66" s="94" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66" s="69"/>
+      <c r="G66" s="90" t="s">
+        <v>125</v>
+      </c>
+      <c r="H66" s="90"/>
+      <c r="I66" s="90"/>
+      <c r="J66" s="90"/>
+      <c r="K66" s="90"/>
+      <c r="L66" s="90"/>
+      <c r="M66" s="90"/>
+      <c r="N66" s="90"/>
+      <c r="O66" s="90"/>
+      <c r="P66" s="90"/>
+      <c r="Q66" s="90"/>
+      <c r="R66" s="90"/>
+      <c r="S66" s="90"/>
+      <c r="T66" s="90"/>
+      <c r="U66" s="90"/>
+      <c r="V66" s="90"/>
+      <c r="W66" s="90"/>
+      <c r="X66" s="90"/>
+      <c r="Y66" s="90"/>
+      <c r="Z66" s="90"/>
+      <c r="AA66" s="90"/>
     </row>
     <row r="67" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="99"/>
+      <c r="A67" s="101"/>
       <c r="B67" s="81"/>
       <c r="C67" s="78"/>
-      <c r="D67" s="60"/>
+      <c r="D67" s="70"/>
       <c r="E67" s="92"/>
-      <c r="F67" s="60"/>
+      <c r="F67" s="70"/>
       <c r="G67" s="91"/>
       <c r="H67" s="91"/>
       <c r="I67" s="91"/>
@@ -4305,12 +4356,12 @@
       <c r="AA67" s="91"/>
     </row>
     <row r="68" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="99"/>
+      <c r="A68" s="101"/>
       <c r="B68" s="81"/>
       <c r="C68" s="78"/>
-      <c r="D68" s="60"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="92"/>
-      <c r="F68" s="60"/>
+      <c r="F68" s="70"/>
       <c r="G68" s="91"/>
       <c r="H68" s="91"/>
       <c r="I68" s="91"/>
@@ -4334,12 +4385,12 @@
       <c r="AA68" s="91"/>
     </row>
     <row r="69" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="99"/>
+      <c r="A69" s="101"/>
       <c r="B69" s="81"/>
       <c r="C69" s="78"/>
-      <c r="D69" s="60"/>
+      <c r="D69" s="70"/>
       <c r="E69" s="92"/>
-      <c r="F69" s="60"/>
+      <c r="F69" s="70"/>
       <c r="G69" s="91"/>
       <c r="H69" s="91"/>
       <c r="I69" s="91"/>
@@ -4362,13 +4413,13 @@
       <c r="Z69" s="91"/>
       <c r="AA69" s="91"/>
     </row>
-    <row r="70" spans="1:27" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="99"/>
+    <row r="70" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="101"/>
       <c r="B70" s="81"/>
       <c r="C70" s="78"/>
-      <c r="D70" s="60"/>
+      <c r="D70" s="70"/>
       <c r="E70" s="92"/>
-      <c r="F70" s="60"/>
+      <c r="F70" s="70"/>
       <c r="G70" s="91"/>
       <c r="H70" s="91"/>
       <c r="I70" s="91"/>
@@ -4391,22 +4442,14 @@
       <c r="Z70" s="91"/>
       <c r="AA70" s="91"/>
     </row>
-    <row r="71" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="99"/>
+    <row r="71" spans="1:27" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="101"/>
       <c r="B71" s="81"/>
       <c r="C71" s="78"/>
-      <c r="D71" s="60">
-        <v>1</v>
-      </c>
-      <c r="E71" s="92" t="s">
-        <v>90</v>
-      </c>
-      <c r="F71" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="G71" s="91" t="s">
-        <v>219</v>
-      </c>
+      <c r="D71" s="70"/>
+      <c r="E71" s="92"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="91"/>
       <c r="H71" s="91"/>
       <c r="I71" s="91"/>
       <c r="J71" s="91"/>
@@ -4428,14 +4471,22 @@
       <c r="Z71" s="91"/>
       <c r="AA71" s="91"/>
     </row>
-    <row r="72" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="99"/>
+    <row r="72" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="101"/>
       <c r="B72" s="81"/>
       <c r="C72" s="78"/>
-      <c r="D72" s="60"/>
-      <c r="E72" s="92"/>
-      <c r="F72" s="60"/>
-      <c r="G72" s="91"/>
+      <c r="D72" s="70">
+        <v>1</v>
+      </c>
+      <c r="E72" s="92" t="s">
+        <v>87</v>
+      </c>
+      <c r="F72" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="G72" s="91" t="s">
+        <v>213</v>
+      </c>
       <c r="H72" s="91"/>
       <c r="I72" s="91"/>
       <c r="J72" s="91"/>
@@ -4458,12 +4509,12 @@
       <c r="AA72" s="91"/>
     </row>
     <row r="73" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="99"/>
+      <c r="A73" s="101"/>
       <c r="B73" s="81"/>
       <c r="C73" s="78"/>
-      <c r="D73" s="60"/>
+      <c r="D73" s="70"/>
       <c r="E73" s="92"/>
-      <c r="F73" s="60"/>
+      <c r="F73" s="70"/>
       <c r="G73" s="91"/>
       <c r="H73" s="91"/>
       <c r="I73" s="91"/>
@@ -4487,12 +4538,12 @@
       <c r="AA73" s="91"/>
     </row>
     <row r="74" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="99"/>
+      <c r="A74" s="101"/>
       <c r="B74" s="81"/>
       <c r="C74" s="78"/>
-      <c r="D74" s="60"/>
+      <c r="D74" s="70"/>
       <c r="E74" s="92"/>
-      <c r="F74" s="60"/>
+      <c r="F74" s="70"/>
       <c r="G74" s="91"/>
       <c r="H74" s="91"/>
       <c r="I74" s="91"/>
@@ -4515,110 +4566,110 @@
       <c r="Z74" s="91"/>
       <c r="AA74" s="91"/>
     </row>
-    <row r="75" spans="1:27" s="3" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="99"/>
-      <c r="B75" s="82"/>
-      <c r="C75" s="79"/>
-      <c r="D75" s="73"/>
-      <c r="E75" s="95"/>
-      <c r="F75" s="73"/>
-      <c r="G75" s="96"/>
-      <c r="H75" s="96"/>
-      <c r="I75" s="96"/>
-      <c r="J75" s="96"/>
-      <c r="K75" s="96"/>
-      <c r="L75" s="96"/>
-      <c r="M75" s="96"/>
-      <c r="N75" s="96"/>
-      <c r="O75" s="96"/>
-      <c r="P75" s="96"/>
-      <c r="Q75" s="96"/>
-      <c r="R75" s="96"/>
-      <c r="S75" s="96"/>
-      <c r="T75" s="96"/>
-      <c r="U75" s="96"/>
-      <c r="V75" s="96"/>
-      <c r="W75" s="96"/>
-      <c r="X75" s="96"/>
-      <c r="Y75" s="96"/>
-      <c r="Z75" s="96"/>
-      <c r="AA75" s="96"/>
-    </row>
-    <row r="76" spans="1:27" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="99"/>
-      <c r="B76" s="80" t="s">
-        <v>65</v>
-      </c>
-      <c r="C76" s="71" t="s">
-        <v>80</v>
-      </c>
-      <c r="D76" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="E76" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="F76" s="97" t="s">
-        <v>89</v>
-      </c>
-      <c r="G76" s="89"/>
-      <c r="H76" s="89"/>
-      <c r="I76" s="89"/>
-      <c r="J76" s="89"/>
-      <c r="K76" s="18"/>
-      <c r="L76" s="18"/>
-      <c r="M76" s="18"/>
-      <c r="N76" s="18"/>
-      <c r="O76" s="18"/>
-      <c r="P76" s="18"/>
-      <c r="Q76" s="18"/>
-      <c r="R76" s="18"/>
-      <c r="S76" s="18"/>
-      <c r="T76" s="18"/>
-      <c r="U76" s="18"/>
-      <c r="V76" s="18"/>
-      <c r="W76" s="18"/>
-      <c r="X76" s="18"/>
-      <c r="Y76" s="18"/>
-      <c r="Z76" s="18"/>
-      <c r="AA76" s="18"/>
-    </row>
-    <row r="77" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="99"/>
-      <c r="B77" s="81"/>
-      <c r="C77" s="78"/>
-      <c r="D77" s="60"/>
-      <c r="E77" s="67"/>
-      <c r="F77" s="59"/>
-      <c r="G77" s="87"/>
-      <c r="H77" s="87"/>
-      <c r="I77" s="87"/>
-      <c r="J77" s="87"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="16"/>
-      <c r="O77" s="16"/>
-      <c r="P77" s="16"/>
-      <c r="Q77" s="16"/>
-      <c r="R77" s="16"/>
-      <c r="S77" s="16"/>
-      <c r="T77" s="16"/>
-      <c r="U77" s="16"/>
-      <c r="V77" s="16"/>
-      <c r="W77" s="16"/>
-      <c r="X77" s="16"/>
-      <c r="Y77" s="16"/>
-      <c r="Z77" s="16"/>
-      <c r="AA77" s="16"/>
+    <row r="75" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="101"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="78"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="92"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="91"/>
+      <c r="H75" s="91"/>
+      <c r="I75" s="91"/>
+      <c r="J75" s="91"/>
+      <c r="K75" s="91"/>
+      <c r="L75" s="91"/>
+      <c r="M75" s="91"/>
+      <c r="N75" s="91"/>
+      <c r="O75" s="91"/>
+      <c r="P75" s="91"/>
+      <c r="Q75" s="91"/>
+      <c r="R75" s="91"/>
+      <c r="S75" s="91"/>
+      <c r="T75" s="91"/>
+      <c r="U75" s="91"/>
+      <c r="V75" s="91"/>
+      <c r="W75" s="91"/>
+      <c r="X75" s="91"/>
+      <c r="Y75" s="91"/>
+      <c r="Z75" s="91"/>
+      <c r="AA75" s="91"/>
+    </row>
+    <row r="76" spans="1:27" s="3" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="101"/>
+      <c r="B76" s="82"/>
+      <c r="C76" s="79"/>
+      <c r="D76" s="76"/>
+      <c r="E76" s="95"/>
+      <c r="F76" s="76"/>
+      <c r="G76" s="96"/>
+      <c r="H76" s="96"/>
+      <c r="I76" s="96"/>
+      <c r="J76" s="96"/>
+      <c r="K76" s="96"/>
+      <c r="L76" s="96"/>
+      <c r="M76" s="96"/>
+      <c r="N76" s="96"/>
+      <c r="O76" s="96"/>
+      <c r="P76" s="96"/>
+      <c r="Q76" s="96"/>
+      <c r="R76" s="96"/>
+      <c r="S76" s="96"/>
+      <c r="T76" s="96"/>
+      <c r="U76" s="96"/>
+      <c r="V76" s="96"/>
+      <c r="W76" s="96"/>
+      <c r="X76" s="96"/>
+      <c r="Y76" s="96"/>
+      <c r="Z76" s="96"/>
+      <c r="AA76" s="96"/>
+    </row>
+    <row r="77" spans="1:27" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="101"/>
+      <c r="B77" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="C77" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="D77" s="69" t="s">
+        <v>88</v>
+      </c>
+      <c r="E77" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="F77" s="97" t="s">
+        <v>260</v>
+      </c>
+      <c r="G77" s="89"/>
+      <c r="H77" s="89"/>
+      <c r="I77" s="89"/>
+      <c r="J77" s="89"/>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
+      <c r="M77" s="18"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="18"/>
+      <c r="P77" s="18"/>
+      <c r="Q77" s="18"/>
+      <c r="R77" s="18"/>
+      <c r="S77" s="18"/>
+      <c r="T77" s="18"/>
+      <c r="U77" s="18"/>
+      <c r="V77" s="18"/>
+      <c r="W77" s="18"/>
+      <c r="X77" s="18"/>
+      <c r="Y77" s="18"/>
+      <c r="Z77" s="18"/>
+      <c r="AA77" s="18"/>
     </row>
     <row r="78" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="99"/>
+      <c r="A78" s="101"/>
       <c r="B78" s="81"/>
       <c r="C78" s="78"/>
-      <c r="D78" s="60"/>
-      <c r="E78" s="67"/>
-      <c r="F78" s="59"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="68"/>
+      <c r="F78" s="72"/>
       <c r="G78" s="87"/>
       <c r="H78" s="87"/>
       <c r="I78" s="87"/>
@@ -4641,17 +4692,13 @@
       <c r="Z78" s="16"/>
       <c r="AA78" s="16"/>
     </row>
-    <row r="79" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="99"/>
+    <row r="79" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="101"/>
       <c r="B79" s="81"/>
       <c r="C79" s="78"/>
-      <c r="D79" s="93" t="s">
-        <v>93</v>
-      </c>
-      <c r="E79" s="92" t="s">
-        <v>82</v>
-      </c>
-      <c r="F79" s="59"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="68"/>
+      <c r="F79" s="72"/>
       <c r="G79" s="87"/>
       <c r="H79" s="87"/>
       <c r="I79" s="87"/>
@@ -4674,13 +4721,17 @@
       <c r="Z79" s="16"/>
       <c r="AA79" s="16"/>
     </row>
-    <row r="80" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="99"/>
+    <row r="80" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="101"/>
       <c r="B80" s="81"/>
       <c r="C80" s="78"/>
-      <c r="D80" s="93"/>
-      <c r="E80" s="92"/>
-      <c r="F80" s="59"/>
+      <c r="D80" s="93" t="s">
+        <v>89</v>
+      </c>
+      <c r="E80" s="92" t="s">
+        <v>80</v>
+      </c>
+      <c r="F80" s="72"/>
       <c r="G80" s="87"/>
       <c r="H80" s="87"/>
       <c r="I80" s="87"/>
@@ -4704,12 +4755,12 @@
       <c r="AA80" s="16"/>
     </row>
     <row r="81" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="99"/>
+      <c r="A81" s="101"/>
       <c r="B81" s="81"/>
       <c r="C81" s="78"/>
       <c r="D81" s="93"/>
       <c r="E81" s="92"/>
-      <c r="F81" s="59"/>
+      <c r="F81" s="72"/>
       <c r="G81" s="87"/>
       <c r="H81" s="87"/>
       <c r="I81" s="87"/>
@@ -4732,19 +4783,13 @@
       <c r="Z81" s="16"/>
       <c r="AA81" s="16"/>
     </row>
-    <row r="82" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="99"/>
+    <row r="82" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="101"/>
       <c r="B82" s="81"/>
       <c r="C82" s="78"/>
-      <c r="D82" s="93" t="s">
-        <v>94</v>
-      </c>
-      <c r="E82" s="101" t="s">
-        <v>83</v>
-      </c>
-      <c r="F82" s="59" t="s">
-        <v>91</v>
-      </c>
+      <c r="D82" s="93"/>
+      <c r="E82" s="92"/>
+      <c r="F82" s="72"/>
       <c r="G82" s="87"/>
       <c r="H82" s="87"/>
       <c r="I82" s="87"/>
@@ -4767,13 +4812,19 @@
       <c r="Z82" s="16"/>
       <c r="AA82" s="16"/>
     </row>
-    <row r="83" spans="1:27" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="99"/>
+    <row r="83" spans="1:27" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="101"/>
       <c r="B83" s="81"/>
       <c r="C83" s="78"/>
-      <c r="D83" s="93"/>
-      <c r="E83" s="101"/>
-      <c r="F83" s="59"/>
+      <c r="D83" s="93" t="s">
+        <v>90</v>
+      </c>
+      <c r="E83" s="103" t="s">
+        <v>81</v>
+      </c>
+      <c r="F83" s="72" t="s">
+        <v>261</v>
+      </c>
       <c r="G83" s="87"/>
       <c r="H83" s="87"/>
       <c r="I83" s="87"/>
@@ -4796,237 +4847,265 @@
       <c r="Z83" s="16"/>
       <c r="AA83" s="16"/>
     </row>
-    <row r="84" spans="1:27" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="99"/>
-      <c r="B84" s="82"/>
-      <c r="C84" s="79"/>
-      <c r="D84" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="E84" s="38" t="s">
+    <row r="84" spans="1:27" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="101"/>
+      <c r="B84" s="81"/>
+      <c r="C84" s="78"/>
+      <c r="D84" s="93"/>
+      <c r="E84" s="103"/>
+      <c r="F84" s="72"/>
+      <c r="G84" s="87"/>
+      <c r="H84" s="87"/>
+      <c r="I84" s="87"/>
+      <c r="J84" s="87"/>
+      <c r="K84" s="16"/>
+      <c r="L84" s="16"/>
+      <c r="M84" s="16"/>
+      <c r="N84" s="16"/>
+      <c r="O84" s="16"/>
+      <c r="P84" s="16"/>
+      <c r="Q84" s="16"/>
+      <c r="R84" s="16"/>
+      <c r="S84" s="16"/>
+      <c r="T84" s="16"/>
+      <c r="U84" s="16"/>
+      <c r="V84" s="16"/>
+      <c r="W84" s="16"/>
+      <c r="X84" s="16"/>
+      <c r="Y84" s="16"/>
+      <c r="Z84" s="16"/>
+      <c r="AA84" s="16"/>
+    </row>
+    <row r="85" spans="1:27" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="101"/>
+      <c r="B85" s="82"/>
+      <c r="C85" s="79"/>
+      <c r="D85" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="F85" s="83"/>
+      <c r="G85" s="88"/>
+      <c r="H85" s="88"/>
+      <c r="I85" s="88"/>
+      <c r="J85" s="88"/>
+      <c r="K85" s="19"/>
+      <c r="L85" s="19"/>
+      <c r="M85" s="19"/>
+      <c r="N85" s="19"/>
+      <c r="O85" s="19"/>
+      <c r="P85" s="19"/>
+      <c r="Q85" s="19"/>
+      <c r="R85" s="19"/>
+      <c r="S85" s="19"/>
+      <c r="T85" s="19"/>
+      <c r="U85" s="19"/>
+      <c r="V85" s="19"/>
+      <c r="W85" s="19"/>
+      <c r="X85" s="19"/>
+      <c r="Y85" s="19"/>
+      <c r="Z85" s="19"/>
+      <c r="AA85" s="19"/>
+    </row>
+    <row r="86" spans="1:27" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="101"/>
+      <c r="B86" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="C86" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="F84" s="83"/>
-      <c r="G84" s="88"/>
-      <c r="H84" s="88"/>
-      <c r="I84" s="88"/>
-      <c r="J84" s="88"/>
-      <c r="K84" s="19"/>
-      <c r="L84" s="19"/>
-      <c r="M84" s="19"/>
-      <c r="N84" s="19"/>
-      <c r="O84" s="19"/>
-      <c r="P84" s="19"/>
-      <c r="Q84" s="19"/>
-      <c r="R84" s="19"/>
-      <c r="S84" s="19"/>
-      <c r="T84" s="19"/>
-      <c r="U84" s="19"/>
-      <c r="V84" s="19"/>
-      <c r="W84" s="19"/>
-      <c r="X84" s="19"/>
-      <c r="Y84" s="19"/>
-      <c r="Z84" s="19"/>
-      <c r="AA84" s="19"/>
-    </row>
-    <row r="85" spans="1:27" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="99"/>
-      <c r="B85" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="C85" s="71" t="s">
-        <v>86</v>
-      </c>
-      <c r="D85" s="68">
+      <c r="D86" s="69">
         <v>0</v>
       </c>
-      <c r="E85" s="94" t="s">
-        <v>87</v>
-      </c>
-      <c r="F85" s="68"/>
-      <c r="G85" s="90" t="s">
-        <v>130</v>
-      </c>
-      <c r="H85" s="90"/>
-      <c r="I85" s="90"/>
-      <c r="J85" s="90"/>
-      <c r="K85" s="90"/>
-      <c r="L85" s="90"/>
-      <c r="M85" s="90"/>
-      <c r="N85" s="90"/>
-      <c r="O85" s="90"/>
-      <c r="P85" s="90"/>
-      <c r="Q85" s="90"/>
-      <c r="R85" s="90"/>
-      <c r="S85" s="90"/>
-      <c r="T85" s="90"/>
-      <c r="U85" s="90"/>
-      <c r="V85" s="90"/>
-      <c r="W85" s="90"/>
-      <c r="X85" s="90"/>
-      <c r="Y85" s="90"/>
-      <c r="Z85" s="90"/>
-      <c r="AA85" s="90"/>
-    </row>
-    <row r="86" spans="1:27" s="2" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="99"/>
-      <c r="B86" s="81"/>
-      <c r="C86" s="78"/>
-      <c r="D86" s="60"/>
-      <c r="E86" s="92"/>
-      <c r="F86" s="60"/>
-      <c r="G86" s="91"/>
-      <c r="H86" s="91"/>
-      <c r="I86" s="91"/>
-      <c r="J86" s="91"/>
-      <c r="K86" s="91"/>
-      <c r="L86" s="91"/>
-      <c r="M86" s="91"/>
-      <c r="N86" s="91"/>
-      <c r="O86" s="91"/>
-      <c r="P86" s="91"/>
-      <c r="Q86" s="91"/>
-      <c r="R86" s="91"/>
-      <c r="S86" s="91"/>
-      <c r="T86" s="91"/>
-      <c r="U86" s="91"/>
-      <c r="V86" s="91"/>
-      <c r="W86" s="91"/>
-      <c r="X86" s="91"/>
-      <c r="Y86" s="91"/>
-      <c r="Z86" s="91"/>
-      <c r="AA86" s="91"/>
-    </row>
-    <row r="87" spans="1:27" s="2" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="99"/>
+      <c r="E86" s="94" t="s">
+        <v>85</v>
+      </c>
+      <c r="F86" s="69"/>
+      <c r="G86" s="90" t="s">
+        <v>125</v>
+      </c>
+      <c r="H86" s="90"/>
+      <c r="I86" s="90"/>
+      <c r="J86" s="90"/>
+      <c r="K86" s="90"/>
+      <c r="L86" s="90"/>
+      <c r="M86" s="90"/>
+      <c r="N86" s="90"/>
+      <c r="O86" s="90"/>
+      <c r="P86" s="90"/>
+      <c r="Q86" s="90"/>
+      <c r="R86" s="90"/>
+      <c r="S86" s="90"/>
+      <c r="T86" s="90"/>
+      <c r="U86" s="90"/>
+      <c r="V86" s="90"/>
+      <c r="W86" s="90"/>
+      <c r="X86" s="90"/>
+      <c r="Y86" s="90"/>
+      <c r="Z86" s="90"/>
+      <c r="AA86" s="90"/>
+    </row>
+    <row r="87" spans="1:27" s="2" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="101"/>
       <c r="B87" s="81"/>
       <c r="C87" s="78"/>
-      <c r="D87" s="60">
+      <c r="D87" s="70"/>
+      <c r="E87" s="92"/>
+      <c r="F87" s="70"/>
+      <c r="G87" s="91"/>
+      <c r="H87" s="91"/>
+      <c r="I87" s="91"/>
+      <c r="J87" s="91"/>
+      <c r="K87" s="91"/>
+      <c r="L87" s="91"/>
+      <c r="M87" s="91"/>
+      <c r="N87" s="91"/>
+      <c r="O87" s="91"/>
+      <c r="P87" s="91"/>
+      <c r="Q87" s="91"/>
+      <c r="R87" s="91"/>
+      <c r="S87" s="91"/>
+      <c r="T87" s="91"/>
+      <c r="U87" s="91"/>
+      <c r="V87" s="91"/>
+      <c r="W87" s="91"/>
+      <c r="X87" s="91"/>
+      <c r="Y87" s="91"/>
+      <c r="Z87" s="91"/>
+      <c r="AA87" s="91"/>
+    </row>
+    <row r="88" spans="1:27" s="2" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="101"/>
+      <c r="B88" s="81"/>
+      <c r="C88" s="78"/>
+      <c r="D88" s="70">
         <v>1</v>
       </c>
-      <c r="E87" s="92" t="s">
-        <v>88</v>
-      </c>
-      <c r="F87" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="G87" s="87"/>
-      <c r="H87" s="87"/>
-      <c r="I87" s="87"/>
-      <c r="J87" s="87"/>
-      <c r="K87" s="16"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="16"/>
-      <c r="N87" s="16"/>
-      <c r="O87" s="16"/>
-      <c r="P87" s="16"/>
-      <c r="Q87" s="16"/>
-      <c r="R87" s="16"/>
-      <c r="S87" s="16"/>
-      <c r="T87" s="16"/>
-      <c r="U87" s="16"/>
-      <c r="V87" s="16"/>
-      <c r="W87" s="16"/>
-      <c r="X87" s="16"/>
-      <c r="Y87" s="16"/>
-      <c r="Z87" s="16"/>
-      <c r="AA87" s="16"/>
-    </row>
-    <row r="88" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="100"/>
-      <c r="B88" s="82"/>
-      <c r="C88" s="79"/>
-      <c r="D88" s="73"/>
-      <c r="E88" s="95"/>
-      <c r="F88" s="83"/>
-      <c r="G88" s="88"/>
-      <c r="H88" s="88"/>
-      <c r="I88" s="88"/>
-      <c r="J88" s="88"/>
-      <c r="K88" s="17"/>
-      <c r="L88" s="17"/>
-      <c r="M88" s="17"/>
-      <c r="N88" s="17"/>
-      <c r="O88" s="17"/>
-      <c r="P88" s="17"/>
-      <c r="Q88" s="17"/>
-      <c r="R88" s="17"/>
-      <c r="S88" s="17"/>
-      <c r="T88" s="17"/>
-      <c r="U88" s="17"/>
-      <c r="V88" s="17"/>
-      <c r="W88" s="17"/>
-      <c r="X88" s="17"/>
-      <c r="Y88" s="17"/>
-      <c r="Z88" s="17"/>
-      <c r="AA88" s="17"/>
+      <c r="E88" s="92" t="s">
+        <v>86</v>
+      </c>
+      <c r="F88" s="72" t="s">
+        <v>260</v>
+      </c>
+      <c r="G88" s="87"/>
+      <c r="H88" s="87"/>
+      <c r="I88" s="87"/>
+      <c r="J88" s="87"/>
+      <c r="K88" s="16"/>
+      <c r="L88" s="16"/>
+      <c r="M88" s="16"/>
+      <c r="N88" s="16"/>
+      <c r="O88" s="16"/>
+      <c r="P88" s="16"/>
+      <c r="Q88" s="16"/>
+      <c r="R88" s="16"/>
+      <c r="S88" s="16"/>
+      <c r="T88" s="16"/>
+      <c r="U88" s="16"/>
+      <c r="V88" s="16"/>
+      <c r="W88" s="16"/>
+      <c r="X88" s="16"/>
+      <c r="Y88" s="16"/>
+      <c r="Z88" s="16"/>
+      <c r="AA88" s="16"/>
+    </row>
+    <row r="89" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="102"/>
+      <c r="B89" s="82"/>
+      <c r="C89" s="79"/>
+      <c r="D89" s="76"/>
+      <c r="E89" s="95"/>
+      <c r="F89" s="83"/>
+      <c r="G89" s="88"/>
+      <c r="H89" s="88"/>
+      <c r="I89" s="88"/>
+      <c r="J89" s="88"/>
+      <c r="K89" s="17"/>
+      <c r="L89" s="17"/>
+      <c r="M89" s="17"/>
+      <c r="N89" s="17"/>
+      <c r="O89" s="17"/>
+      <c r="P89" s="17"/>
+      <c r="Q89" s="17"/>
+      <c r="R89" s="17"/>
+      <c r="S89" s="17"/>
+      <c r="T89" s="17"/>
+      <c r="U89" s="17"/>
+      <c r="V89" s="17"/>
+      <c r="W89" s="17"/>
+      <c r="X89" s="17"/>
+      <c r="Y89" s="17"/>
+      <c r="Z89" s="17"/>
+      <c r="AA89" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="101">
-    <mergeCell ref="E47:E53"/>
-    <mergeCell ref="D47:D53"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="A36:A64"/>
-    <mergeCell ref="G63:I64"/>
-    <mergeCell ref="E59:E62"/>
-    <mergeCell ref="D59:D62"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="B59:B64"/>
-    <mergeCell ref="C59:C64"/>
+  <mergeCells count="103">
+    <mergeCell ref="A36:A65"/>
+    <mergeCell ref="G64:I65"/>
+    <mergeCell ref="E60:E63"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B60:B65"/>
+    <mergeCell ref="C60:C65"/>
     <mergeCell ref="C36:C46"/>
     <mergeCell ref="B36:B46"/>
     <mergeCell ref="F36:F39"/>
     <mergeCell ref="F40:F46"/>
     <mergeCell ref="F47:F53"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="C57:C59"/>
     <mergeCell ref="F54:F55"/>
-    <mergeCell ref="A65:A88"/>
-    <mergeCell ref="F65:F70"/>
-    <mergeCell ref="F71:F75"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:F84"/>
-    <mergeCell ref="B65:B75"/>
-    <mergeCell ref="C65:C75"/>
-    <mergeCell ref="B76:B84"/>
-    <mergeCell ref="C76:C84"/>
-    <mergeCell ref="B85:B88"/>
-    <mergeCell ref="C85:C88"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="G87:J88"/>
-    <mergeCell ref="G76:J78"/>
-    <mergeCell ref="G79:J81"/>
-    <mergeCell ref="G82:J83"/>
-    <mergeCell ref="G84:J84"/>
-    <mergeCell ref="G85:AA86"/>
-    <mergeCell ref="G65:AA70"/>
-    <mergeCell ref="E76:E78"/>
-    <mergeCell ref="E79:E81"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="E65:E70"/>
-    <mergeCell ref="E71:E75"/>
-    <mergeCell ref="G71:AA75"/>
-    <mergeCell ref="F76:F81"/>
-    <mergeCell ref="D65:D70"/>
-    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="E40:E46"/>
+    <mergeCell ref="D40:D46"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="A66:A89"/>
+    <mergeCell ref="F66:F71"/>
+    <mergeCell ref="F72:F76"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="F83:F85"/>
+    <mergeCell ref="B66:B76"/>
+    <mergeCell ref="C66:C76"/>
+    <mergeCell ref="B77:B85"/>
+    <mergeCell ref="C77:C85"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="E47:E53"/>
+    <mergeCell ref="D47:D53"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="E66:E71"/>
+    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="G72:AA76"/>
+    <mergeCell ref="F77:F82"/>
+    <mergeCell ref="D66:D71"/>
+    <mergeCell ref="D72:D76"/>
     <mergeCell ref="B47:B56"/>
     <mergeCell ref="C47:C56"/>
-    <mergeCell ref="E36:E39"/>
-    <mergeCell ref="D36:D39"/>
-    <mergeCell ref="E40:E46"/>
-    <mergeCell ref="D40:D46"/>
+    <mergeCell ref="G88:J89"/>
+    <mergeCell ref="G77:J79"/>
+    <mergeCell ref="G80:J82"/>
+    <mergeCell ref="G83:J84"/>
+    <mergeCell ref="G85:J85"/>
+    <mergeCell ref="G86:AA87"/>
+    <mergeCell ref="G66:AA71"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="E80:E82"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="C22:C25"/>
     <mergeCell ref="C13:C21"/>
@@ -5064,6 +5143,9 @@
     <mergeCell ref="D10:D12"/>
     <mergeCell ref="E10:E12"/>
     <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="B32:B35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5085,32 +5167,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5322,598 +5404,598 @@
   <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="47" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="48"/>
-    <col min="3" max="3" width="9.140625" style="47"/>
-    <col min="4" max="4" width="9.140625" style="46"/>
-    <col min="5" max="5" width="25.85546875" style="49" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="49" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="44"/>
+    <col min="1" max="1" width="11.140625" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="47"/>
+    <col min="3" max="3" width="9.140625" style="46"/>
+    <col min="4" max="4" width="9.140625" style="45"/>
+    <col min="5" max="5" width="25.85546875" style="48" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="43"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="119" t="s">
         <v>35</v>
       </c>
       <c r="C1" s="120"/>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="41" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="132" t="s">
+      <c r="A2" s="121" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="127" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" s="130" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="114">
+        <v>0</v>
+      </c>
+      <c r="E2" s="112" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="114"/>
+      <c r="G2" s="42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="122"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="125" t="s">
+    </row>
+    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="122"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="42" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="122"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="114">
+        <v>1</v>
+      </c>
+      <c r="E5" s="112" t="s">
+        <v>220</v>
+      </c>
+      <c r="F5" s="114"/>
+      <c r="G5" s="42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="122"/>
+      <c r="B6" s="128"/>
+      <c r="C6" s="131"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="42" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="122"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="42" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="122"/>
+      <c r="B8" s="128"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="114">
+        <v>3</v>
+      </c>
+      <c r="E8" s="112" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" s="116"/>
+      <c r="G8" s="43" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="122"/>
+      <c r="B9" s="128"/>
+      <c r="C9" s="131"/>
+      <c r="D9" s="114"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="43" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="122"/>
+      <c r="B10" s="128"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="43" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="122"/>
+      <c r="B11" s="128"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="43" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="123"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="50">
+        <v>4</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="F12" s="51"/>
+      <c r="G12" s="52" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="124" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="127" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" s="133" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="138">
+        <v>0</v>
+      </c>
+      <c r="E13" s="118" t="s">
+        <v>222</v>
+      </c>
+      <c r="F13" s="117"/>
+      <c r="G13" s="43" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="125"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="134"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="43" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="125"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="43" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="125"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="134"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="J16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="125"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="114">
+        <v>1</v>
+      </c>
+      <c r="E17" s="112" t="s">
+        <v>223</v>
+      </c>
+      <c r="F17" s="112" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="54" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="125"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="114"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="54" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="125"/>
+      <c r="B19" s="136"/>
+      <c r="C19" s="134"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="54" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="125"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="134"/>
+      <c r="D20" s="114"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="54" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="125"/>
+      <c r="B21" s="136"/>
+      <c r="C21" s="134"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="54" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="116" t="s">
-        <v>127</v>
-      </c>
-      <c r="D2" s="110">
-        <v>0</v>
-      </c>
-      <c r="E2" s="111" t="s">
-        <v>227</v>
-      </c>
-      <c r="F2" s="110"/>
-      <c r="G2" s="43" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="133"/>
-      <c r="B3" s="114"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="43" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="133"/>
-      <c r="B4" s="114"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="43" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="133"/>
-      <c r="B5" s="114"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="110">
-        <v>1</v>
-      </c>
-      <c r="E5" s="111" t="s">
-        <v>226</v>
-      </c>
-      <c r="F5" s="110"/>
-      <c r="G5" s="43" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="133"/>
-      <c r="B6" s="114"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="43" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="133"/>
-      <c r="B7" s="114"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="43" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="133"/>
-      <c r="B8" s="114"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="110">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="125"/>
+      <c r="B22" s="136"/>
+      <c r="C22" s="134"/>
+      <c r="D22" s="114"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="54" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="125"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="134"/>
+      <c r="D23" s="114"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="54" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="125"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="134"/>
+      <c r="D24" s="114"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="54" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="125"/>
+      <c r="B25" s="136"/>
+      <c r="C25" s="134"/>
+      <c r="D25" s="114">
+        <v>2</v>
+      </c>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="54" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="125"/>
+      <c r="B26" s="136"/>
+      <c r="C26" s="134"/>
+      <c r="D26" s="114"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="54" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="125"/>
+      <c r="B27" s="136"/>
+      <c r="C27" s="134"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="54" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="125"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="134"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="54" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="125"/>
+      <c r="B29" s="136"/>
+      <c r="C29" s="134"/>
+      <c r="D29" s="114"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="54" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="125"/>
+      <c r="B30" s="136"/>
+      <c r="C30" s="134"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="54" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="125"/>
+      <c r="B31" s="136"/>
+      <c r="C31" s="134"/>
+      <c r="D31" s="114"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="54" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="125"/>
+      <c r="B32" s="136"/>
+      <c r="C32" s="134"/>
+      <c r="D32" s="114"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="54" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="125"/>
+      <c r="B33" s="136"/>
+      <c r="C33" s="134"/>
+      <c r="D33" s="114">
         <v>3</v>
       </c>
-      <c r="E8" s="111" t="s">
-        <v>225</v>
-      </c>
-      <c r="F8" s="112"/>
-      <c r="G8" s="44" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="133"/>
-      <c r="B9" s="114"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="44" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="133"/>
-      <c r="B10" s="114"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="44" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="133"/>
-      <c r="B11" s="114"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="44" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="134"/>
-      <c r="B12" s="115"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="51">
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="54" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="125"/>
+      <c r="B34" s="136"/>
+      <c r="C34" s="134"/>
+      <c r="D34" s="114"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="54" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="125"/>
+      <c r="B35" s="136"/>
+      <c r="C35" s="134"/>
+      <c r="D35" s="114"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="54" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="125"/>
+      <c r="B36" s="136"/>
+      <c r="C36" s="134"/>
+      <c r="D36" s="114"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="54" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="125"/>
+      <c r="B37" s="136"/>
+      <c r="C37" s="134"/>
+      <c r="D37" s="114"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="54" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="125"/>
+      <c r="B38" s="136"/>
+      <c r="C38" s="134"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="112"/>
+      <c r="F38" s="112"/>
+      <c r="G38" s="54" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="125"/>
+      <c r="B39" s="136"/>
+      <c r="C39" s="134"/>
+      <c r="D39" s="114"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="54" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="125"/>
+      <c r="B40" s="136"/>
+      <c r="C40" s="134"/>
+      <c r="D40" s="114"/>
+      <c r="E40" s="112"/>
+      <c r="F40" s="112"/>
+      <c r="G40" s="54" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="125"/>
+      <c r="B41" s="136"/>
+      <c r="C41" s="134"/>
+      <c r="D41" s="114">
         <v>4</v>
       </c>
-      <c r="E12" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="F12" s="52"/>
-      <c r="G12" s="53" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="135" t="s">
-        <v>193</v>
-      </c>
-      <c r="B13" s="125" t="s">
-        <v>232</v>
-      </c>
-      <c r="C13" s="121" t="s">
-        <v>230</v>
-      </c>
-      <c r="D13" s="109">
-        <v>0</v>
-      </c>
-      <c r="E13" s="126" t="s">
-        <v>228</v>
-      </c>
-      <c r="F13" s="113"/>
-      <c r="G13" s="44" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="136"/>
-      <c r="B14" s="124"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="112"/>
-      <c r="G14" s="44" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="136"/>
-      <c r="B15" s="124"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="112"/>
-      <c r="G15" s="44" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="136"/>
-      <c r="B16" s="124"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="44" t="s">
-        <v>223</v>
-      </c>
-      <c r="J16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="136"/>
-      <c r="B17" s="124"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="110">
-        <v>1</v>
-      </c>
-      <c r="E17" s="111" t="s">
-        <v>229</v>
-      </c>
-      <c r="F17" s="111" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="130" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="136"/>
-      <c r="B18" s="124"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="111"/>
-      <c r="G18" s="130" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="136"/>
-      <c r="B19" s="124"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="130" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="136"/>
-      <c r="B20" s="124"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="130" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="136"/>
-      <c r="B21" s="124"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="130" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="136"/>
-      <c r="B22" s="124"/>
-      <c r="C22" s="122"/>
-      <c r="D22" s="110"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="130" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="136"/>
-      <c r="B23" s="124"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="130" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="136"/>
-      <c r="B24" s="124"/>
-      <c r="C24" s="122"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="130" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="136"/>
-      <c r="B25" s="124"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="110">
-        <v>2</v>
-      </c>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="130" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="136"/>
-      <c r="B26" s="124"/>
-      <c r="C26" s="122"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="130" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="136"/>
-      <c r="B27" s="124"/>
-      <c r="C27" s="122"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="130" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="136"/>
-      <c r="B28" s="124"/>
-      <c r="C28" s="122"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="130" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="136"/>
-      <c r="B29" s="124"/>
-      <c r="C29" s="122"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="130" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="136"/>
-      <c r="B30" s="124"/>
-      <c r="C30" s="122"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="111"/>
-      <c r="G30" s="130" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="136"/>
-      <c r="B31" s="124"/>
-      <c r="C31" s="122"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="111"/>
-      <c r="G31" s="130" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="136"/>
-      <c r="B32" s="124"/>
-      <c r="C32" s="122"/>
-      <c r="D32" s="110"/>
-      <c r="E32" s="111"/>
-      <c r="F32" s="111"/>
-      <c r="G32" s="130" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="136"/>
-      <c r="B33" s="124"/>
-      <c r="C33" s="122"/>
-      <c r="D33" s="110">
-        <v>3</v>
-      </c>
-      <c r="E33" s="111"/>
-      <c r="F33" s="111"/>
-      <c r="G33" s="130" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="136"/>
-      <c r="B34" s="124"/>
-      <c r="C34" s="122"/>
-      <c r="D34" s="110"/>
-      <c r="E34" s="111"/>
-      <c r="F34" s="111"/>
-      <c r="G34" s="130" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="136"/>
-      <c r="B35" s="124"/>
-      <c r="C35" s="122"/>
-      <c r="D35" s="110"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
-      <c r="G35" s="130" t="s">
+      <c r="E41" s="112"/>
+      <c r="F41" s="112"/>
+      <c r="G41" s="54" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="136"/>
-      <c r="B36" s="124"/>
-      <c r="C36" s="122"/>
-      <c r="D36" s="110"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="130" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="125"/>
+      <c r="B42" s="136"/>
+      <c r="C42" s="134"/>
+      <c r="D42" s="114"/>
+      <c r="E42" s="112"/>
+      <c r="F42" s="112"/>
+      <c r="G42" s="54" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="136"/>
-      <c r="B37" s="124"/>
-      <c r="C37" s="122"/>
-      <c r="D37" s="110"/>
-      <c r="E37" s="111"/>
-      <c r="F37" s="111"/>
-      <c r="G37" s="130" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="125"/>
+      <c r="B43" s="136"/>
+      <c r="C43" s="134"/>
+      <c r="D43" s="114"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="54" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="136"/>
-      <c r="B38" s="124"/>
-      <c r="C38" s="122"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="111"/>
-      <c r="F38" s="111"/>
-      <c r="G38" s="130" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="125"/>
+      <c r="B44" s="136"/>
+      <c r="C44" s="134"/>
+      <c r="D44" s="114"/>
+      <c r="E44" s="112"/>
+      <c r="F44" s="112"/>
+      <c r="G44" s="54" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="136"/>
-      <c r="B39" s="124"/>
-      <c r="C39" s="122"/>
-      <c r="D39" s="110"/>
-      <c r="E39" s="111"/>
-      <c r="F39" s="111"/>
-      <c r="G39" s="130" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="125"/>
+      <c r="B45" s="136"/>
+      <c r="C45" s="134"/>
+      <c r="D45" s="114"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="54" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="136"/>
-      <c r="B40" s="124"/>
-      <c r="C40" s="122"/>
-      <c r="D40" s="110"/>
-      <c r="E40" s="111"/>
-      <c r="F40" s="111"/>
-      <c r="G40" s="130" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="125"/>
+      <c r="B46" s="136"/>
+      <c r="C46" s="134"/>
+      <c r="D46" s="114"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="54" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="136"/>
-      <c r="B41" s="124"/>
-      <c r="C41" s="122"/>
-      <c r="D41" s="110">
-        <v>4</v>
-      </c>
-      <c r="E41" s="111"/>
-      <c r="F41" s="111"/>
-      <c r="G41" s="130" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="125"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="134"/>
+      <c r="D47" s="114"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="54" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="136"/>
-      <c r="B42" s="124"/>
-      <c r="C42" s="122"/>
-      <c r="D42" s="110"/>
-      <c r="E42" s="111"/>
-      <c r="F42" s="111"/>
-      <c r="G42" s="130" t="s">
+    <row r="48" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="126"/>
+      <c r="B48" s="137"/>
+      <c r="C48" s="135"/>
+      <c r="D48" s="115"/>
+      <c r="E48" s="113"/>
+      <c r="F48" s="113"/>
+      <c r="G48" s="55" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="136"/>
-      <c r="B43" s="124"/>
-      <c r="C43" s="122"/>
-      <c r="D43" s="110"/>
-      <c r="E43" s="111"/>
-      <c r="F43" s="111"/>
-      <c r="G43" s="130" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="136"/>
-      <c r="B44" s="124"/>
-      <c r="C44" s="122"/>
-      <c r="D44" s="110"/>
-      <c r="E44" s="111"/>
-      <c r="F44" s="111"/>
-      <c r="G44" s="130" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="136"/>
-      <c r="B45" s="124"/>
-      <c r="C45" s="122"/>
-      <c r="D45" s="110"/>
-      <c r="E45" s="111"/>
-      <c r="F45" s="111"/>
-      <c r="G45" s="130" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="136"/>
-      <c r="B46" s="124"/>
-      <c r="C46" s="122"/>
-      <c r="D46" s="110"/>
-      <c r="E46" s="111"/>
-      <c r="F46" s="111"/>
-      <c r="G46" s="130" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="136"/>
-      <c r="B47" s="124"/>
-      <c r="C47" s="122"/>
-      <c r="D47" s="110"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="130" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="137"/>
-      <c r="B48" s="127"/>
-      <c r="C48" s="123"/>
-      <c r="D48" s="128"/>
-      <c r="E48" s="129"/>
-      <c r="F48" s="129"/>
-      <c r="G48" s="131" t="s">
-        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -5923,21 +6005,21 @@
     <mergeCell ref="D8:D11"/>
     <mergeCell ref="B2:B12"/>
     <mergeCell ref="C2:C12"/>
+    <mergeCell ref="C13:C48"/>
+    <mergeCell ref="B13:B48"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="D17:D24"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="F5:F7"/>
+    <mergeCell ref="E2:E4"/>
     <mergeCell ref="F8:F11"/>
     <mergeCell ref="F13:F16"/>
     <mergeCell ref="E13:E16"/>
     <mergeCell ref="E8:E11"/>
     <mergeCell ref="E5:E7"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="C13:C48"/>
-    <mergeCell ref="B13:B48"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="D17:D24"/>
     <mergeCell ref="F17:F48"/>
     <mergeCell ref="E17:E48"/>
     <mergeCell ref="D25:D32"/>
